--- a/data/trans_orig/P04B1_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279314</t>
+          <t>280871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>330715</t>
+          <t>330934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>173454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217558</t>
+          <t>218755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>467218</t>
+          <t>470345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>538908</t>
+          <t>536735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69272</t>
+          <t>69053</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120673</t>
+          <t>119116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114450</t>
+          <t>114451</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93907</t>
+          <t>92711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137083</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172544</t>
+          <t>174717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244234</t>
+          <t>241107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311465</t>
+          <t>311466</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311465</t>
+          <t>311466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311465</t>
+          <t>311466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258268</t>
+          <t>255288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>305167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335058</t>
+          <t>336846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>424901</t>
+          <t>419712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>610719</t>
+          <t>611473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>721583</t>
+          <t>709320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116213</t>
+          <t>118215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165114</t>
+          <t>168094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87192</t>
+          <t>92381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177035</t>
+          <t>175247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213892</t>
+          <t>226155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324756</t>
+          <t>324002</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>349257</t>
+          <t>351279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>395128</t>
+          <t>392560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>398288</t>
+          <t>397190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>464137</t>
+          <t>462618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>760308</t>
+          <t>763603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>839522</t>
+          <t>843746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,96%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140179</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>186050</t>
+          <t>184028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126199</t>
+          <t>127718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>192048</t>
+          <t>193146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286121</t>
+          <t>281897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365335</t>
+          <t>362040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>615670</t>
+          <t>618035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>799928</t>
+          <t>802389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>461054</t>
+          <t>461783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>522663</t>
+          <t>519300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1099079</t>
+          <t>1094540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1367052</t>
+          <t>1349952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272116</t>
+          <t>269751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188072</t>
+          <t>191435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249681</t>
+          <t>248952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231470</t>
+          <t>248570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>499443</t>
+          <t>503982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>354326</t>
+          <t>354791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>395487</t>
+          <t>393859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>340361</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>375148</t>
+          <t>374534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>705272</t>
+          <t>708182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>759728</t>
+          <t>759356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162439</t>
+          <t>164067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203600</t>
+          <t>203135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172137</t>
+          <t>172751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206924</t>
+          <t>204613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345484</t>
+          <t>345856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399940</t>
+          <t>397030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>230378</t>
+          <t>229873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>259113</t>
+          <t>259219</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>399446</t>
+          <t>398360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>552755</t>
+          <t>553704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>640412</t>
+          <t>641255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>846258</t>
+          <t>839747</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108273</t>
+          <t>108167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137008</t>
+          <t>137513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208343</t>
+          <t>209429</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128917</t>
+          <t>135428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>334763</t>
+          <t>333920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171925</t>
+          <t>172732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197998</t>
+          <t>197720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>274094</t>
+          <t>273896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302688</t>
+          <t>301327</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>455826</t>
+          <t>452536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>490443</t>
+          <t>492346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84761</t>
+          <t>85039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110834</t>
+          <t>110027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122543</t>
+          <t>123904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>151335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217547</t>
+          <t>215644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252164</t>
+          <t>255454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2369539</t>
+          <t>2372691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2678590</t>
+          <t>2678784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2497834</t>
+          <t>2488685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2806501</t>
+          <t>2800898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4908917</t>
+          <t>4909939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5325501</t>
+          <t>5309435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>775944</t>
+          <t>775750</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1084995</t>
+          <t>1081843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>898434</t>
+          <t>904037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1207101</t>
+          <t>1216250</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1833968</t>
+          <t>1850034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2250552</t>
+          <t>2249530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>307784</t>
+          <t>288586</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>280871</t>
+          <t>260293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>330934</t>
+          <t>314945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>197015</t>
+          <t>220709</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173454</t>
+          <t>194972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218755</t>
+          <t>244099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>504799</t>
+          <t>509295</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>470345</t>
+          <t>469149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>536735</t>
+          <t>545966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92203</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119116</t>
+          <t>147500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114451</t>
+          <t>140096</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92711</t>
+          <t>116706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138012</t>
+          <t>165833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>206653</t>
+          <t>259303</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174717</t>
+          <t>222632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241107</t>
+          <t>299449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311466</t>
+          <t>360805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311466</t>
+          <t>360805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311466</t>
+          <t>360805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>711452</t>
+          <t>768598</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711452</t>
+          <t>768598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711452</t>
+          <t>768598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>282480</t>
+          <t>312774</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>255288</t>
+          <t>286069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>305167</t>
+          <t>339306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>367586</t>
+          <t>329070</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336846</t>
+          <t>306081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>419712</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>650066</t>
+          <t>641844</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611473</t>
+          <t>609104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>709320</t>
+          <t>675799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>140902</t>
+          <t>162473</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118215</t>
+          <t>135941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168094</t>
+          <t>189178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>144507</t>
+          <t>172663</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92381</t>
+          <t>149888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175247</t>
+          <t>195652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>285409</t>
+          <t>335136</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226155</t>
+          <t>301181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324002</t>
+          <t>367876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935475</t>
+          <t>976980</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935475</t>
+          <t>976980</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935475</t>
+          <t>976980</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>372265</t>
+          <t>422676</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351279</t>
+          <t>397371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>392560</t>
+          <t>445525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>421661</t>
+          <t>429034</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>397190</t>
+          <t>409292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>462618</t>
+          <t>448591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>793926</t>
+          <t>851710</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>763603</t>
+          <t>817679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>843746</t>
+          <t>882115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>163042</t>
+          <t>196145</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142747</t>
+          <t>173296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184028</t>
+          <t>221450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>168675</t>
+          <t>191617</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127718</t>
+          <t>172060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>193146</t>
+          <t>211359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>331717</t>
+          <t>387762</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281897</t>
+          <t>357357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362040</t>
+          <t>421793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535307</t>
+          <t>618821</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535307</t>
+          <t>618821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535307</t>
+          <t>618821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>590336</t>
+          <t>620651</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>590336</t>
+          <t>620651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>590336</t>
+          <t>620651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1125643</t>
+          <t>1239472</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1125643</t>
+          <t>1239472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1125643</t>
+          <t>1239472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>700088</t>
+          <t>486571</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>618035</t>
+          <t>458388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>802389</t>
+          <t>509434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>484108</t>
+          <t>474933</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>461783</t>
+          <t>455069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>519300</t>
+          <t>497848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1184196</t>
+          <t>961505</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1094540</t>
+          <t>929214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1349952</t>
+          <t>997547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>187698</t>
+          <t>214046</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85397</t>
+          <t>191183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269751</t>
+          <t>242229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>226627</t>
+          <t>259158</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191435</t>
+          <t>236243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248952</t>
+          <t>279022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>414326</t>
+          <t>473204</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248570</t>
+          <t>437162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>503982</t>
+          <t>505495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>710735</t>
+          <t>734091</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>710735</t>
+          <t>734091</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>710735</t>
+          <t>734091</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598522</t>
+          <t>1434709</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598522</t>
+          <t>1434709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598522</t>
+          <t>1434709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>375494</t>
+          <t>402030</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>354791</t>
+          <t>379248</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>393859</t>
+          <t>422712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>358201</t>
+          <t>389036</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>370012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374534</t>
+          <t>407611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>733696</t>
+          <t>791066</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>708182</t>
+          <t>760339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>759356</t>
+          <t>819177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>182432</t>
+          <t>203769</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164067</t>
+          <t>183087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203135</t>
+          <t>226551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>189084</t>
+          <t>219112</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172751</t>
+          <t>200537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204613</t>
+          <t>238136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>371516</t>
+          <t>422880</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345856</t>
+          <t>394769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>397030</t>
+          <t>453607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>557926</t>
+          <t>605799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557926</t>
+          <t>605799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557926</t>
+          <t>605799</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105212</t>
+          <t>1213946</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105212</t>
+          <t>1213946</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105212</t>
+          <t>1213946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>244932</t>
+          <t>270265</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>229873</t>
+          <t>252654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>259219</t>
+          <t>285444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>473127</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>398360</t>
+          <t>272681</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>553704</t>
+          <t>300640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>718059</t>
+          <t>557284</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>641255</t>
+          <t>535397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>839747</t>
+          <t>577415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>122454</t>
+          <t>135812</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108167</t>
+          <t>120633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137513</t>
+          <t>153423</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>134662</t>
+          <t>151458</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>137838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209429</t>
+          <t>165797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>257116</t>
+          <t>287270</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135428</t>
+          <t>267139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>333920</t>
+          <t>309157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367386</t>
+          <t>406077</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367386</t>
+          <t>406077</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367386</t>
+          <t>406077</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975175</t>
+          <t>844554</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975175</t>
+          <t>844554</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975175</t>
+          <t>844554</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>185017</t>
+          <t>200191</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172732</t>
+          <t>186460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197720</t>
+          <t>213734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>288008</t>
+          <t>309246</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>273896</t>
+          <t>293759</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301327</t>
+          <t>324270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>473025</t>
+          <t>509437</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>452536</t>
+          <t>488288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>492346</t>
+          <t>528517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97742</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85039</t>
+          <t>96464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110027</t>
+          <t>123738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>137223</t>
+          <t>154716</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123904</t>
+          <t>139692</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151335</t>
+          <t>170203</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>234965</t>
+          <t>264723</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215644</t>
+          <t>245643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>255454</t>
+          <t>285872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425231</t>
+          <t>463962</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707990</t>
+          <t>774160</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707990</t>
+          <t>774160</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707990</t>
+          <t>774160</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2468061</t>
+          <t>2383093</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2372691</t>
+          <t>2327305</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2678784</t>
+          <t>2444983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2589706</t>
+          <t>2439047</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2488685</t>
+          <t>2385894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2800898</t>
+          <t>2493646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5057767</t>
+          <t>4822141</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4909939</t>
+          <t>4744488</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5309435</t>
+          <t>4899166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>986473</t>
+          <t>1141460</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>775750</t>
+          <t>1079570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1081843</t>
+          <t>1197248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1115229</t>
+          <t>1288820</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>904037</t>
+          <t>1234221</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1216250</t>
+          <t>1341973</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2101702</t>
+          <t>2430279</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1850034</t>
+          <t>2353254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2249530</t>
+          <t>2507932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454534</t>
+          <t>3524553</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3704935</t>
+          <t>3727867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7159469</t>
+          <t>7252420</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
